--- a/survey_templates/045_online_platform_user_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/045_online_platform_user_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>overall_rating</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rating_comment</t>
+          <t>user_experience</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rating Comment</t>
+          <t>User Experience</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,22 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>experience</t>
+          <t>issues_encountered</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>User Experience</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>e.g., user interface, navigation, performance</t>
-        </is>
-      </c>
+          <t>Issues Encountered</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -616,22 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>issues</t>
+          <t>any_suggestions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Issues Encountered</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Describe any issues you have encountered.</t>
-        </is>
-      </c>
+          <t>Any Suggestions?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -643,22 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>recommendations</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Recommendations</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Any suggestions for improvement?</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -670,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -693,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Overall Satisfaction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -716,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>additional_feedback</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +715,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -747,14 +735,10 @@
           <t>Select Multiple</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -777,7 +761,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -853,165 +837,161 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>email_repeat</t>
+          <t>select_multiple_repeat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Select Multiple Repeat</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>phone_repeat</t>
+          <t>select_one_repeat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Select One Repeat</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>select_multiple_repeat</t>
+          <t>overall_satisfaction_repeat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+          <t>Overall Satisfaction Repeat</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>select_one_repeat</t>
+          <t>feedback_repeat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Feedback Repeat</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>date_repeat</t>
+          <t>select_multiple_repeat_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Select Multiple Repeat 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>time_repeat</t>
+          <t>select_one_repeat_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Select One Repeat 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>note_repeat</t>
+          <t>overall_satisfaction_repeat_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Overall Satisfaction Repeat 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1023,18 +1003,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>platform_name_repeat</t>
+          <t>feedback_repeat_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Platform Name</t>
+          <t>Feedback Repeat 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1046,18 +1026,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>rating_repeat</t>
+          <t>improvement_needed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Overall Rating (1-5)</t>
+          <t>Improvement Needed</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1069,22 +1049,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>experience_repeat</t>
+          <t>email_repeat</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>User Experience</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>e.g., user interface, navigation, performance</t>
-        </is>
-      </c>
+          <t>Email Repeat</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1096,49 +1072,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>issues_repeat</t>
+          <t>phone_repeat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Issues Encountered</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Describe any issues you have encountered.</t>
-        </is>
-      </c>
+          <t>Phone Repeat</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>recommendations_repeat</t>
+          <t>note_repeat</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Recommendations</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Any suggestions for improvement?</t>
-        </is>
-      </c>
+          <t>Note Repeat</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1150,18 +1118,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>email_repeat</t>
+          <t>overall_satisfaction_repeat_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Overall Satisfaction Repeat 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1173,18 +1141,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>phone_repeat</t>
+          <t>feedback_repeat_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Feedback Repeat 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1196,425 +1164,64 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>feedback_repeat</t>
+          <t>improvement_repeat</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Additional Feedback</t>
+          <t>Improvement Repeat</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>select_multiple_repeat</t>
+          <t>overall_satisfaction_repeat_3_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
+          <t>Overall Satisfaction Repeat 3 2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>select_one_repeat</t>
+          <t>feedback_repeat_3_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Feedback Repeat 3 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>date_repeat</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>time_repeat</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>note_repeat</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>platform_name_repeat</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Platform Name</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>overall_satisfaction</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Overall Satisfaction</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>On a scale of 1-10</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>improvement_needed</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Improvement Needed</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Describe any areas of improvement</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>email_repeat</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>phone_repeat</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>select_multiple_repeat</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Select all that apply</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>select_one_repeat</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>date_repeat</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>time_repeat</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>note_repeat</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>platform_name_repeat</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Platform Name</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_repeat</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Overall Satisfaction</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1236,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1662,12 +1269,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1286,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1303,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1320,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1337,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1354,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1371,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1388,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1405,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1422,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1439,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
@@ -1849,216 +1456,114 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple_repeat_choices</t>
+          <t>select_multiple_repeat_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple_repeat_choices</t>
+          <t>select_multiple_repeat_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple_repeat_choices</t>
+          <t>select_multiple_repeat_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one_repeat_choices</t>
+          <t>select_one_repeat_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one_repeat_choices</t>
+          <t>select_one_repeat_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one_repeat_choices</t>
+          <t>select_one_repeat_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple_repeat_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple_repeat_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple_repeat_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one_repeat_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one_repeat_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one_repeat_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
